--- a/source/APPN/TD_APPN_Common.xlsx
+++ b/source/APPN/TD_APPN_Common.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="230">
   <si>
     <t xml:space="preserve">APPN Adelaide University vocabularies</t>
   </si>
@@ -1035,6 +1035,12 @@
     <t xml:space="preserve">http://purl.obolibrary.org/obo/PO_0030117</t>
   </si>
   <si>
+    <t xml:space="preserve">cohort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An ObservationUnit comprising multiple plants of the same BiologicalMaterial and receiving the same treatment</t>
+  </si>
+  <si>
     <t xml:space="preserve">genus</t>
   </si>
   <si>
@@ -1326,7 +1332,13 @@
     <t xml:space="preserve">whole tree chamber</t>
   </si>
   <si>
-    <t xml:space="preserve">Whole tree chambers are controlled-environment systems that enclose individual trees, either potted or rooted in soil, within large structures exposed to natural sunlight. These chambers enable precise regulation of atmospheric conditions such as carbon dioxide, temperature, and humidity, while continuously measuring gas exchange between the tree canopy and the surrounding air. Designed for field-based research, they support experiments that simulate climate change conditions and allow detailed study of whole-tree responses at high temporal resolution.</t>
+    <t xml:space="preserve">Whole Tree Chambers provide fully enclosed, controlled environments for trees up to nine metres tall. In these chambers, researchers can manipulate the environment around a tree including air temperature, soil moisture, irrigation, CO2 levels and humidity to predict the integrated effects of altered climates on tree physiology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pots are containers for soil and growth mixtures in which a single plant can be grown.</t>
   </si>
 </sst>
 </file>
@@ -2123,100 +2135,100 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="244">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2224,287 +2236,287 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="9" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="9" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="11" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="9" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="9" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2512,15 +2524,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2528,563 +2540,575 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="22" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="22" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="22" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="23" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="23" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="25" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="25" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="25" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="25" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="25" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="26" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="26" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="27" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="27" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="27" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="27" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="27" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="27" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="27" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="27" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="27" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="27" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="27" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="27" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="28" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="28" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="29" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="29" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="29" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="29" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="29" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="29" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="29" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="29" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="29" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="30" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="30" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="30" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="30" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="32" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3208,37 +3232,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3568,52 +3592,52 @@
         <v>29</v>
       </c>
       <c r="C1" s="146" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="147" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B2" s="148"/>
       <c r="C2" s="149" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="150" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="149" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="152" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" s="148"/>
       <c r="C4" s="149" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="153" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B5" s="151"/>
       <c r="C5" s="149" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="154" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B6" s="155"/>
       <c r="C6" s="156" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3721,141 +3745,141 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="158" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="158" width="46.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="158" width="52.63"/>
   </cols>
   <sheetData>
-    <row r="1" s="161" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="158" t="s">
+    <row r="1" s="162" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="159" t="s">
+      <c r="B1" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="160" t="s">
+      <c r="C1" s="161" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="162"/>
-      <c r="B2" s="163"/>
-      <c r="C2" s="164"/>
+      <c r="A2" s="163"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="165"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="165"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="167"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="168"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="168"/>
-      <c r="B4" s="169"/>
-      <c r="C4" s="167"/>
+      <c r="A4" s="169"/>
+      <c r="B4" s="170"/>
+      <c r="C4" s="168"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="170"/>
-      <c r="B5" s="170"/>
-      <c r="C5" s="170"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="171"/>
+      <c r="C5" s="171"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="170"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="170"/>
+      <c r="A6" s="171"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="171"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="170"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
+      <c r="A7" s="171"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="171"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="170"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="170"/>
+      <c r="A8" s="171"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="171"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="170"/>
-      <c r="B9" s="170"/>
-      <c r="C9" s="170"/>
+      <c r="A9" s="171"/>
+      <c r="B9" s="171"/>
+      <c r="C9" s="171"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="170"/>
-      <c r="B10" s="170"/>
-      <c r="C10" s="170"/>
+      <c r="A10" s="171"/>
+      <c r="B10" s="171"/>
+      <c r="C10" s="171"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="170"/>
-      <c r="B11" s="170"/>
-      <c r="C11" s="170"/>
+      <c r="A11" s="171"/>
+      <c r="B11" s="171"/>
+      <c r="C11" s="171"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="170"/>
-      <c r="B12" s="170"/>
-      <c r="C12" s="170"/>
+      <c r="A12" s="171"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="171"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="170"/>
-      <c r="B13" s="170"/>
-      <c r="C13" s="170"/>
+      <c r="A13" s="171"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="171"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="170"/>
-      <c r="B14" s="170"/>
-      <c r="C14" s="170"/>
+      <c r="A14" s="171"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="170"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
+      <c r="A15" s="171"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="170"/>
-      <c r="B16" s="170"/>
-      <c r="C16" s="170"/>
+      <c r="A16" s="171"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="170"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="170"/>
+      <c r="A17" s="171"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="171"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="170"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="170"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="171"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="170"/>
-      <c r="B19" s="170"/>
-      <c r="C19" s="170"/>
+      <c r="A19" s="171"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="171"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="170"/>
-      <c r="B20" s="170"/>
-      <c r="C20" s="170"/>
+      <c r="A20" s="171"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="171"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="170"/>
-      <c r="B21" s="170"/>
-      <c r="C21" s="170"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="171"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="170"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="170"/>
+      <c r="A22" s="171"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="171"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="170"/>
-      <c r="B23" s="170"/>
-      <c r="C23" s="170"/>
+      <c r="A23" s="171"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="171"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="170"/>
-      <c r="B24" s="170"/>
-      <c r="C24" s="170"/>
+      <c r="A24" s="171"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="171"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="170"/>
-      <c r="B25" s="170"/>
-      <c r="C25" s="170"/>
+      <c r="A25" s="171"/>
+      <c r="B25" s="171"/>
+      <c r="C25" s="171"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3877,1211 +3901,1211 @@
   <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="42.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="158" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="158" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="158" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="158" width="25.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="158" width="35.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="158" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="158" width="23.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="158" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="158" width="26.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="158" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="158" width="42.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="158" width="32.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="158" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="158" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="158" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="158" width="26.75"/>
   </cols>
   <sheetData>
-    <row r="1" s="182" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="171" t="s">
+    <row r="1" s="183" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="172" t="s">
+      <c r="B1" s="173" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="173" t="s">
-        <v>196</v>
-      </c>
-      <c r="D1" s="174" t="s">
-        <v>197</v>
-      </c>
-      <c r="E1" s="175" t="s">
+      <c r="C1" s="174" t="s">
         <v>198</v>
       </c>
-      <c r="F1" s="176" t="s">
+      <c r="D1" s="175" t="s">
         <v>199</v>
       </c>
-      <c r="G1" s="175" t="s">
+      <c r="E1" s="176" t="s">
         <v>200</v>
       </c>
-      <c r="H1" s="174" t="s">
+      <c r="F1" s="177" t="s">
         <v>201</v>
       </c>
-      <c r="I1" s="177" t="s">
+      <c r="G1" s="176" t="s">
         <v>202</v>
       </c>
-      <c r="J1" s="175" t="s">
+      <c r="H1" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="K1" s="174" t="s">
+      <c r="I1" s="178" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1" s="176" t="s">
+        <v>205</v>
+      </c>
+      <c r="K1" s="175" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="173" t="s">
-        <v>171</v>
-      </c>
-      <c r="M1" s="178" t="s">
-        <v>172</v>
-      </c>
-      <c r="N1" s="179" t="s">
+      <c r="L1" s="174" t="s">
         <v>173</v>
       </c>
-      <c r="O1" s="180" t="s">
-        <v>204</v>
-      </c>
-      <c r="P1" s="171" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q1" s="181"/>
+      <c r="M1" s="179" t="s">
+        <v>174</v>
+      </c>
+      <c r="N1" s="180" t="s">
+        <v>175</v>
+      </c>
+      <c r="O1" s="181" t="s">
+        <v>206</v>
+      </c>
+      <c r="P1" s="172" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q1" s="182"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="183"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="189"/>
-      <c r="M2" s="191"/>
-      <c r="N2" s="191"/>
-      <c r="O2" s="190"/>
-      <c r="P2" s="189"/>
-      <c r="Q2" s="192"/>
+      <c r="A2" s="184"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="192"/>
+      <c r="N2" s="192"/>
+      <c r="O2" s="191"/>
+      <c r="P2" s="190"/>
+      <c r="Q2" s="193"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="193"/>
-      <c r="B3" s="194"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="186"/>
-      <c r="I3" s="197"/>
-      <c r="J3" s="197"/>
-      <c r="K3" s="197"/>
-      <c r="L3" s="190"/>
-      <c r="M3" s="197"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="198"/>
-      <c r="Q3" s="199"/>
+      <c r="A3" s="194"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="198"/>
+      <c r="N3" s="199"/>
+      <c r="O3" s="191"/>
+      <c r="P3" s="199"/>
+      <c r="Q3" s="200"/>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="183"/>
-      <c r="B4" s="194"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="196"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="197"/>
-      <c r="J4" s="197"/>
-      <c r="K4" s="197"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="197"/>
-      <c r="N4" s="198"/>
-      <c r="O4" s="190"/>
-      <c r="P4" s="198"/>
-      <c r="Q4" s="199"/>
+      <c r="A4" s="184"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="197"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="198"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="198"/>
+      <c r="L4" s="191"/>
+      <c r="M4" s="198"/>
+      <c r="N4" s="199"/>
+      <c r="O4" s="191"/>
+      <c r="P4" s="199"/>
+      <c r="Q4" s="200"/>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="200"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="186"/>
-      <c r="I5" s="197"/>
-      <c r="J5" s="197"/>
-      <c r="K5" s="197"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="197"/>
-      <c r="N5" s="198"/>
-      <c r="O5" s="190"/>
-      <c r="P5" s="198"/>
-      <c r="Q5" s="199"/>
+      <c r="A5" s="201"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="203"/>
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="187"/>
+      <c r="G5" s="197"/>
+      <c r="H5" s="187"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="198"/>
+      <c r="N5" s="199"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="199"/>
+      <c r="Q5" s="200"/>
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="193"/>
-      <c r="B6" s="187"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="186"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="197"/>
-      <c r="K6" s="197"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="204"/>
-      <c r="N6" s="205"/>
-      <c r="O6" s="190"/>
-      <c r="P6" s="205"/>
-      <c r="Q6" s="199"/>
+      <c r="A6" s="194"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="204"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="197"/>
+      <c r="H6" s="187"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="198"/>
+      <c r="K6" s="198"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="205"/>
+      <c r="N6" s="206"/>
+      <c r="O6" s="191"/>
+      <c r="P6" s="206"/>
+      <c r="Q6" s="200"/>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="206"/>
-      <c r="B7" s="207"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="204"/>
-      <c r="K7" s="204"/>
-      <c r="L7" s="190"/>
-      <c r="M7" s="204"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="190"/>
-      <c r="P7" s="205"/>
+      <c r="A7" s="207"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="187"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="197"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="206"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="205"/>
+      <c r="N7" s="206"/>
+      <c r="O7" s="191"/>
+      <c r="P7" s="206"/>
       <c r="Q7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="208"/>
-      <c r="B8" s="184"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="196"/>
-      <c r="H8" s="186"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="204"/>
-      <c r="L8" s="190"/>
-      <c r="M8" s="197"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="190"/>
-      <c r="P8" s="198"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="185"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="197"/>
+      <c r="H8" s="187"/>
+      <c r="I8" s="206"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="205"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="199"/>
+      <c r="O8" s="191"/>
+      <c r="P8" s="199"/>
       <c r="Q8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="209"/>
-      <c r="B9" s="210"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="196"/>
-      <c r="H9" s="186"/>
-      <c r="I9" s="205"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="204"/>
-      <c r="L9" s="190"/>
-      <c r="M9" s="204"/>
-      <c r="N9" s="205"/>
-      <c r="O9" s="190"/>
-      <c r="P9" s="211"/>
+      <c r="A9" s="210"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="197"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="206"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="205"/>
+      <c r="L9" s="191"/>
+      <c r="M9" s="205"/>
+      <c r="N9" s="206"/>
+      <c r="O9" s="191"/>
+      <c r="P9" s="212"/>
       <c r="Q9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="209"/>
-      <c r="B10" s="212"/>
-      <c r="C10" s="195"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="186"/>
-      <c r="G10" s="196"/>
-      <c r="H10" s="186"/>
-      <c r="I10" s="205"/>
-      <c r="J10" s="204"/>
-      <c r="K10" s="204"/>
-      <c r="L10" s="190"/>
-      <c r="M10" s="204"/>
-      <c r="N10" s="205"/>
-      <c r="O10" s="190"/>
-      <c r="P10" s="211"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="213"/>
+      <c r="C10" s="196"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="197"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="206"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="191"/>
+      <c r="M10" s="205"/>
+      <c r="N10" s="206"/>
+      <c r="O10" s="191"/>
+      <c r="P10" s="212"/>
       <c r="Q10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="209"/>
-      <c r="B11" s="213"/>
-      <c r="C11" s="195"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="186"/>
-      <c r="F11" s="186"/>
-      <c r="G11" s="196"/>
-      <c r="H11" s="186"/>
-      <c r="I11" s="205"/>
-      <c r="J11" s="204"/>
-      <c r="K11" s="204"/>
-      <c r="L11" s="190"/>
-      <c r="M11" s="204"/>
-      <c r="N11" s="205"/>
-      <c r="O11" s="190"/>
-      <c r="P11" s="211"/>
+      <c r="A11" s="210"/>
+      <c r="B11" s="214"/>
+      <c r="C11" s="196"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="187"/>
+      <c r="F11" s="187"/>
+      <c r="G11" s="197"/>
+      <c r="H11" s="187"/>
+      <c r="I11" s="206"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="205"/>
+      <c r="L11" s="191"/>
+      <c r="M11" s="205"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="191"/>
+      <c r="P11" s="212"/>
       <c r="Q11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="209"/>
-      <c r="B12" s="210"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="196"/>
-      <c r="H12" s="186"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="204"/>
-      <c r="K12" s="204"/>
-      <c r="L12" s="190"/>
-      <c r="M12" s="204"/>
-      <c r="N12" s="205"/>
-      <c r="O12" s="190"/>
-      <c r="P12" s="211"/>
+      <c r="A12" s="210"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="196"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="197"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="206"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="191"/>
+      <c r="M12" s="205"/>
+      <c r="N12" s="206"/>
+      <c r="O12" s="191"/>
+      <c r="P12" s="212"/>
       <c r="Q12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="209"/>
-      <c r="B13" s="184"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-      <c r="F13" s="186"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="186"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="204"/>
-      <c r="K13" s="204"/>
-      <c r="L13" s="190"/>
-      <c r="M13" s="204"/>
-      <c r="N13" s="205"/>
-      <c r="O13" s="190"/>
-      <c r="P13" s="205"/>
+      <c r="A13" s="210"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="197"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="206"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="205"/>
+      <c r="L13" s="191"/>
+      <c r="M13" s="205"/>
+      <c r="N13" s="206"/>
+      <c r="O13" s="191"/>
+      <c r="P13" s="206"/>
       <c r="Q13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="209"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
-      <c r="F14" s="186"/>
-      <c r="G14" s="196"/>
-      <c r="H14" s="186"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="204"/>
-      <c r="K14" s="204"/>
-      <c r="L14" s="190"/>
-      <c r="M14" s="204"/>
-      <c r="N14" s="205"/>
-      <c r="O14" s="190"/>
-      <c r="P14" s="205"/>
+      <c r="A14" s="210"/>
+      <c r="B14" s="215"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="187"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="197"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="206"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="191"/>
+      <c r="M14" s="205"/>
+      <c r="N14" s="206"/>
+      <c r="O14" s="191"/>
+      <c r="P14" s="206"/>
       <c r="Q14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="209"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="195"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
-      <c r="G15" s="196"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="205"/>
-      <c r="J15" s="204"/>
-      <c r="K15" s="204"/>
-      <c r="L15" s="190"/>
-      <c r="M15" s="204"/>
-      <c r="N15" s="205"/>
-      <c r="O15" s="190"/>
-      <c r="P15" s="205"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="202"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="197"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="206"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="205"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="191"/>
+      <c r="P15" s="206"/>
       <c r="Q15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="209"/>
-      <c r="B16" s="207"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="186"/>
-      <c r="I16" s="205"/>
-      <c r="J16" s="204"/>
-      <c r="K16" s="204"/>
-      <c r="L16" s="190"/>
-      <c r="M16" s="204"/>
-      <c r="N16" s="205"/>
-      <c r="O16" s="190"/>
-      <c r="P16" s="205"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="197"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="206"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="191"/>
+      <c r="M16" s="205"/>
+      <c r="N16" s="206"/>
+      <c r="O16" s="191"/>
+      <c r="P16" s="206"/>
       <c r="Q16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="209"/>
-      <c r="B17" s="207"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="186"/>
-      <c r="E17" s="186"/>
-      <c r="F17" s="186"/>
-      <c r="G17" s="196"/>
-      <c r="H17" s="186"/>
-      <c r="I17" s="205"/>
-      <c r="J17" s="204"/>
-      <c r="K17" s="204"/>
-      <c r="L17" s="190"/>
-      <c r="M17" s="204"/>
-      <c r="N17" s="205"/>
-      <c r="O17" s="190"/>
-      <c r="P17" s="205"/>
+      <c r="A17" s="210"/>
+      <c r="B17" s="208"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="187"/>
+      <c r="G17" s="197"/>
+      <c r="H17" s="187"/>
+      <c r="I17" s="206"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="205"/>
+      <c r="L17" s="191"/>
+      <c r="M17" s="205"/>
+      <c r="N17" s="206"/>
+      <c r="O17" s="191"/>
+      <c r="P17" s="206"/>
       <c r="Q17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="209"/>
-      <c r="B18" s="184"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="186"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="186"/>
-      <c r="G18" s="196"/>
-      <c r="H18" s="186"/>
-      <c r="I18" s="205"/>
-      <c r="J18" s="204"/>
-      <c r="K18" s="204"/>
-      <c r="L18" s="190"/>
-      <c r="M18" s="204"/>
-      <c r="N18" s="205"/>
-      <c r="O18" s="190"/>
-      <c r="P18" s="205"/>
+      <c r="A18" s="210"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="187"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="197"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="206"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="205"/>
+      <c r="L18" s="191"/>
+      <c r="M18" s="205"/>
+      <c r="N18" s="206"/>
+      <c r="O18" s="191"/>
+      <c r="P18" s="206"/>
       <c r="Q18" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="209"/>
-      <c r="B19" s="194"/>
-      <c r="C19" s="185"/>
-      <c r="D19" s="186"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="186"/>
-      <c r="G19" s="196"/>
-      <c r="H19" s="186"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="204"/>
-      <c r="K19" s="204"/>
-      <c r="L19" s="190"/>
-      <c r="M19" s="204"/>
-      <c r="N19" s="205"/>
-      <c r="O19" s="190"/>
-      <c r="P19" s="205"/>
+      <c r="A19" s="210"/>
+      <c r="B19" s="195"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="187"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="197"/>
+      <c r="H19" s="187"/>
+      <c r="I19" s="206"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="191"/>
+      <c r="M19" s="205"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="191"/>
+      <c r="P19" s="206"/>
       <c r="Q19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="209"/>
-      <c r="B20" s="201"/>
-      <c r="C20" s="195"/>
-      <c r="D20" s="186"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="186"/>
-      <c r="G20" s="186"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="204"/>
-      <c r="K20" s="204"/>
-      <c r="L20" s="190"/>
-      <c r="M20" s="204"/>
-      <c r="N20" s="205"/>
-      <c r="O20" s="190"/>
-      <c r="P20" s="205"/>
+      <c r="A20" s="210"/>
+      <c r="B20" s="202"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="187"/>
+      <c r="E20" s="187"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="187"/>
+      <c r="I20" s="206"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="191"/>
+      <c r="M20" s="205"/>
+      <c r="N20" s="206"/>
+      <c r="O20" s="191"/>
+      <c r="P20" s="206"/>
       <c r="Q20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="209"/>
-      <c r="B21" s="184"/>
-      <c r="C21" s="202"/>
-      <c r="D21" s="186"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="186"/>
-      <c r="G21" s="196"/>
-      <c r="H21" s="186"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="204"/>
-      <c r="K21" s="204"/>
-      <c r="L21" s="190"/>
-      <c r="M21" s="204"/>
-      <c r="N21" s="205"/>
-      <c r="O21" s="190"/>
-      <c r="P21" s="205"/>
+      <c r="A21" s="210"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="197"/>
+      <c r="H21" s="187"/>
+      <c r="I21" s="206"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="205"/>
+      <c r="L21" s="191"/>
+      <c r="M21" s="205"/>
+      <c r="N21" s="206"/>
+      <c r="O21" s="191"/>
+      <c r="P21" s="206"/>
       <c r="Q21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="209"/>
-      <c r="B22" s="194"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="186"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="186"/>
-      <c r="G22" s="196"/>
-      <c r="H22" s="186"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="204"/>
-      <c r="K22" s="204"/>
-      <c r="L22" s="190"/>
-      <c r="M22" s="204"/>
-      <c r="N22" s="205"/>
-      <c r="O22" s="190"/>
-      <c r="P22" s="205"/>
+      <c r="A22" s="210"/>
+      <c r="B22" s="195"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="187"/>
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="187"/>
+      <c r="I22" s="206"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="205"/>
+      <c r="L22" s="191"/>
+      <c r="M22" s="205"/>
+      <c r="N22" s="206"/>
+      <c r="O22" s="191"/>
+      <c r="P22" s="206"/>
       <c r="Q22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="215"/>
-      <c r="B23" s="201"/>
-      <c r="C23" s="195"/>
-      <c r="D23" s="186"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="186"/>
-      <c r="G23" s="196"/>
-      <c r="H23" s="186"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="204"/>
-      <c r="K23" s="204"/>
-      <c r="L23" s="190"/>
-      <c r="M23" s="204"/>
-      <c r="N23" s="205"/>
-      <c r="O23" s="190"/>
-      <c r="P23" s="205"/>
+      <c r="A23" s="216"/>
+      <c r="B23" s="202"/>
+      <c r="C23" s="196"/>
+      <c r="D23" s="187"/>
+      <c r="E23" s="187"/>
+      <c r="F23" s="187"/>
+      <c r="G23" s="197"/>
+      <c r="H23" s="187"/>
+      <c r="I23" s="206"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="205"/>
+      <c r="L23" s="191"/>
+      <c r="M23" s="205"/>
+      <c r="N23" s="206"/>
+      <c r="O23" s="191"/>
+      <c r="P23" s="206"/>
       <c r="Q23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="216"/>
-      <c r="B24" s="184"/>
-      <c r="C24" s="195"/>
-      <c r="D24" s="186"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="186"/>
-      <c r="G24" s="196"/>
-      <c r="H24" s="186"/>
-      <c r="I24" s="205"/>
-      <c r="J24" s="204"/>
-      <c r="K24" s="186"/>
-      <c r="L24" s="190"/>
-      <c r="M24" s="204"/>
-      <c r="N24" s="205"/>
-      <c r="O24" s="190"/>
-      <c r="P24" s="205"/>
+      <c r="A24" s="217"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="196"/>
+      <c r="D24" s="187"/>
+      <c r="E24" s="187"/>
+      <c r="F24" s="187"/>
+      <c r="G24" s="197"/>
+      <c r="H24" s="187"/>
+      <c r="I24" s="206"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="187"/>
+      <c r="L24" s="191"/>
+      <c r="M24" s="205"/>
+      <c r="N24" s="206"/>
+      <c r="O24" s="191"/>
+      <c r="P24" s="206"/>
       <c r="Q24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="215"/>
-      <c r="B25" s="201"/>
-      <c r="C25" s="195"/>
-      <c r="D25" s="186"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="186"/>
-      <c r="G25" s="196"/>
-      <c r="H25" s="186"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="204"/>
-      <c r="K25" s="204"/>
-      <c r="L25" s="190"/>
-      <c r="M25" s="204"/>
-      <c r="N25" s="205"/>
-      <c r="O25" s="190"/>
-      <c r="P25" s="205"/>
+      <c r="A25" s="216"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="187"/>
+      <c r="E25" s="187"/>
+      <c r="F25" s="187"/>
+      <c r="G25" s="197"/>
+      <c r="H25" s="187"/>
+      <c r="I25" s="206"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="205"/>
+      <c r="L25" s="191"/>
+      <c r="M25" s="205"/>
+      <c r="N25" s="206"/>
+      <c r="O25" s="191"/>
+      <c r="P25" s="206"/>
       <c r="Q25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="206"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="195"/>
-      <c r="D26" s="186"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="186"/>
-      <c r="G26" s="196"/>
-      <c r="H26" s="186"/>
-      <c r="I26" s="205"/>
-      <c r="J26" s="204"/>
-      <c r="K26" s="186"/>
-      <c r="L26" s="190"/>
-      <c r="M26" s="204"/>
-      <c r="N26" s="205"/>
-      <c r="O26" s="190"/>
-      <c r="P26" s="205"/>
+      <c r="A26" s="207"/>
+      <c r="B26" s="185"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="197"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="206"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="187"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="205"/>
+      <c r="N26" s="206"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="206"/>
       <c r="Q26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="209"/>
-      <c r="B27" s="194"/>
-      <c r="C27" s="195"/>
-      <c r="D27" s="186"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="186"/>
-      <c r="G27" s="196"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="204"/>
-      <c r="K27" s="204"/>
-      <c r="L27" s="190"/>
-      <c r="M27" s="204"/>
-      <c r="N27" s="205"/>
-      <c r="O27" s="190"/>
-      <c r="P27" s="205"/>
+      <c r="A27" s="210"/>
+      <c r="B27" s="195"/>
+      <c r="C27" s="196"/>
+      <c r="D27" s="187"/>
+      <c r="E27" s="187"/>
+      <c r="F27" s="187"/>
+      <c r="G27" s="197"/>
+      <c r="H27" s="187"/>
+      <c r="I27" s="206"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="205"/>
+      <c r="L27" s="191"/>
+      <c r="M27" s="205"/>
+      <c r="N27" s="206"/>
+      <c r="O27" s="191"/>
+      <c r="P27" s="206"/>
       <c r="Q27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="215"/>
-      <c r="B28" s="217"/>
-      <c r="C28" s="195"/>
-      <c r="D28" s="186"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="186"/>
-      <c r="I28" s="205"/>
-      <c r="J28" s="204"/>
-      <c r="K28" s="204"/>
-      <c r="L28" s="190"/>
-      <c r="M28" s="204"/>
-      <c r="N28" s="205"/>
-      <c r="O28" s="190"/>
-      <c r="P28" s="211"/>
+      <c r="A28" s="216"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="187"/>
+      <c r="E28" s="187"/>
+      <c r="F28" s="187"/>
+      <c r="G28" s="197"/>
+      <c r="H28" s="187"/>
+      <c r="I28" s="206"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="191"/>
+      <c r="M28" s="205"/>
+      <c r="N28" s="206"/>
+      <c r="O28" s="191"/>
+      <c r="P28" s="212"/>
       <c r="Q28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="218"/>
-      <c r="B29" s="217"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="186"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="186"/>
-      <c r="G29" s="196"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="205"/>
-      <c r="J29" s="204"/>
-      <c r="K29" s="204"/>
-      <c r="L29" s="190"/>
-      <c r="M29" s="204"/>
-      <c r="N29" s="205"/>
-      <c r="O29" s="190"/>
-      <c r="P29" s="211"/>
+      <c r="A29" s="219"/>
+      <c r="B29" s="218"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="187"/>
+      <c r="E29" s="187"/>
+      <c r="F29" s="187"/>
+      <c r="G29" s="197"/>
+      <c r="H29" s="187"/>
+      <c r="I29" s="206"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="205"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="205"/>
+      <c r="N29" s="206"/>
+      <c r="O29" s="191"/>
+      <c r="P29" s="212"/>
       <c r="Q29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="218"/>
-      <c r="B30" s="194"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="186"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="186"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="186"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="204"/>
-      <c r="K30" s="204"/>
-      <c r="L30" s="190"/>
-      <c r="M30" s="204"/>
-      <c r="N30" s="205"/>
-      <c r="O30" s="190"/>
-      <c r="P30" s="205"/>
+      <c r="A30" s="219"/>
+      <c r="B30" s="195"/>
+      <c r="C30" s="186"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="187"/>
+      <c r="G30" s="197"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="206"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="191"/>
+      <c r="M30" s="205"/>
+      <c r="N30" s="206"/>
+      <c r="O30" s="191"/>
+      <c r="P30" s="206"/>
       <c r="Q30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="218"/>
-      <c r="B31" s="194"/>
-      <c r="C31" s="195"/>
-      <c r="D31" s="186"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="186"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="186"/>
-      <c r="I31" s="205"/>
-      <c r="J31" s="204"/>
-      <c r="K31" s="204"/>
-      <c r="L31" s="190"/>
-      <c r="M31" s="204"/>
-      <c r="N31" s="205"/>
-      <c r="O31" s="190"/>
-      <c r="P31" s="205"/>
+      <c r="A31" s="219"/>
+      <c r="B31" s="195"/>
+      <c r="C31" s="196"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="187"/>
+      <c r="G31" s="197"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="206"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="191"/>
+      <c r="M31" s="205"/>
+      <c r="N31" s="206"/>
+      <c r="O31" s="191"/>
+      <c r="P31" s="206"/>
       <c r="Q31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="218"/>
-      <c r="B32" s="201"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="186"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="186"/>
-      <c r="G32" s="196"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="204"/>
-      <c r="K32" s="204"/>
-      <c r="L32" s="190"/>
-      <c r="M32" s="204"/>
-      <c r="N32" s="205"/>
-      <c r="O32" s="190"/>
-      <c r="P32" s="205"/>
+      <c r="A32" s="219"/>
+      <c r="B32" s="202"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="187"/>
+      <c r="E32" s="187"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="191"/>
+      <c r="M32" s="205"/>
+      <c r="N32" s="206"/>
+      <c r="O32" s="191"/>
+      <c r="P32" s="206"/>
       <c r="Q32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="218"/>
-      <c r="B33" s="184"/>
-      <c r="C33" s="185"/>
-      <c r="D33" s="186"/>
-      <c r="E33" s="186"/>
-      <c r="F33" s="186"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="186"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="204"/>
-      <c r="K33" s="204"/>
-      <c r="L33" s="190"/>
-      <c r="M33" s="204"/>
-      <c r="N33" s="205"/>
-      <c r="O33" s="190"/>
-      <c r="P33" s="205"/>
+      <c r="A33" s="219"/>
+      <c r="B33" s="185"/>
+      <c r="C33" s="186"/>
+      <c r="D33" s="187"/>
+      <c r="E33" s="187"/>
+      <c r="F33" s="187"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="187"/>
+      <c r="I33" s="206"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="191"/>
+      <c r="M33" s="205"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="191"/>
+      <c r="P33" s="206"/>
       <c r="Q33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="218"/>
-      <c r="B34" s="194"/>
-      <c r="C34" s="195"/>
-      <c r="D34" s="186"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="186"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="204"/>
-      <c r="L34" s="190"/>
-      <c r="M34" s="204"/>
-      <c r="N34" s="205"/>
-      <c r="O34" s="190"/>
-      <c r="P34" s="205"/>
+      <c r="A34" s="219"/>
+      <c r="B34" s="195"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="187"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="206"/>
+      <c r="J34" s="205"/>
+      <c r="K34" s="205"/>
+      <c r="L34" s="191"/>
+      <c r="M34" s="205"/>
+      <c r="N34" s="206"/>
+      <c r="O34" s="191"/>
+      <c r="P34" s="206"/>
       <c r="Q34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="216"/>
-      <c r="B35" s="194"/>
-      <c r="C35" s="202"/>
-      <c r="D35" s="186"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="186"/>
-      <c r="I35" s="205"/>
-      <c r="J35" s="204"/>
-      <c r="K35" s="204"/>
-      <c r="L35" s="190"/>
-      <c r="M35" s="204"/>
-      <c r="N35" s="205"/>
-      <c r="O35" s="190"/>
-      <c r="P35" s="205"/>
+      <c r="A35" s="217"/>
+      <c r="B35" s="195"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="187"/>
+      <c r="E35" s="187"/>
+      <c r="F35" s="187"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="187"/>
+      <c r="I35" s="206"/>
+      <c r="J35" s="205"/>
+      <c r="K35" s="205"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="205"/>
+      <c r="N35" s="206"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="206"/>
       <c r="Q35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="215"/>
-      <c r="B36" s="194"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="204"/>
-      <c r="G36" s="196"/>
-      <c r="H36" s="186"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="204"/>
-      <c r="K36" s="204"/>
-      <c r="L36" s="190"/>
-      <c r="M36" s="204"/>
-      <c r="N36" s="205"/>
-      <c r="O36" s="190"/>
-      <c r="P36" s="205"/>
+      <c r="A36" s="216"/>
+      <c r="B36" s="195"/>
+      <c r="C36" s="186"/>
+      <c r="D36" s="187"/>
+      <c r="E36" s="187"/>
+      <c r="F36" s="205"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="206"/>
+      <c r="J36" s="205"/>
+      <c r="K36" s="205"/>
+      <c r="L36" s="191"/>
+      <c r="M36" s="205"/>
+      <c r="N36" s="206"/>
+      <c r="O36" s="191"/>
+      <c r="P36" s="206"/>
       <c r="Q36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="219"/>
-      <c r="B37" s="201"/>
-      <c r="C37" s="195"/>
-      <c r="D37" s="186"/>
-      <c r="E37" s="186"/>
-      <c r="F37" s="186"/>
-      <c r="G37" s="196"/>
-      <c r="H37" s="186"/>
-      <c r="I37" s="220"/>
-      <c r="J37" s="220"/>
-      <c r="K37" s="204"/>
-      <c r="L37" s="190"/>
-      <c r="M37" s="220"/>
-      <c r="N37" s="211"/>
-      <c r="O37" s="211"/>
-      <c r="P37" s="211"/>
-      <c r="Q37" s="221"/>
+      <c r="A37" s="220"/>
+      <c r="B37" s="202"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="187"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="221"/>
+      <c r="K37" s="205"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="221"/>
+      <c r="N37" s="212"/>
+      <c r="O37" s="212"/>
+      <c r="P37" s="212"/>
+      <c r="Q37" s="222"/>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="222"/>
-      <c r="B38" s="184"/>
-      <c r="C38" s="195"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="196"/>
-      <c r="H38" s="186"/>
-      <c r="I38" s="220"/>
-      <c r="J38" s="220"/>
-      <c r="K38" s="204"/>
-      <c r="L38" s="190"/>
-      <c r="M38" s="220"/>
-      <c r="N38" s="211"/>
-      <c r="O38" s="211"/>
-      <c r="P38" s="211"/>
-      <c r="Q38" s="221"/>
+      <c r="A38" s="223"/>
+      <c r="B38" s="185"/>
+      <c r="C38" s="196"/>
+      <c r="D38" s="187"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="187"/>
+      <c r="I38" s="221"/>
+      <c r="J38" s="221"/>
+      <c r="K38" s="205"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="221"/>
+      <c r="N38" s="212"/>
+      <c r="O38" s="212"/>
+      <c r="P38" s="212"/>
+      <c r="Q38" s="222"/>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="223"/>
-      <c r="B39" s="201"/>
-      <c r="C39" s="202"/>
-      <c r="D39" s="186"/>
-      <c r="E39" s="186"/>
-      <c r="F39" s="186"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="186"/>
-      <c r="I39" s="220"/>
-      <c r="J39" s="220"/>
-      <c r="K39" s="204"/>
-      <c r="L39" s="190"/>
-      <c r="M39" s="220"/>
-      <c r="N39" s="211"/>
-      <c r="O39" s="211"/>
-      <c r="P39" s="211"/>
-      <c r="Q39" s="221"/>
+      <c r="A39" s="224"/>
+      <c r="B39" s="202"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="187"/>
+      <c r="E39" s="187"/>
+      <c r="F39" s="187"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="187"/>
+      <c r="I39" s="221"/>
+      <c r="J39" s="221"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="221"/>
+      <c r="N39" s="212"/>
+      <c r="O39" s="212"/>
+      <c r="P39" s="212"/>
+      <c r="Q39" s="222"/>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="219"/>
-      <c r="B40" s="184"/>
-      <c r="C40" s="224"/>
-      <c r="D40" s="186"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186"/>
-      <c r="G40" s="196"/>
-      <c r="H40" s="186"/>
-      <c r="I40" s="220"/>
-      <c r="J40" s="220"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="190"/>
-      <c r="M40" s="220"/>
-      <c r="N40" s="211"/>
-      <c r="O40" s="211"/>
-      <c r="P40" s="211"/>
-      <c r="Q40" s="221"/>
+      <c r="A40" s="220"/>
+      <c r="B40" s="185"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="187"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="187"/>
+      <c r="I40" s="221"/>
+      <c r="J40" s="221"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="221"/>
+      <c r="N40" s="212"/>
+      <c r="O40" s="212"/>
+      <c r="P40" s="212"/>
+      <c r="Q40" s="222"/>
     </row>
     <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="219"/>
-      <c r="B41" s="201"/>
-      <c r="C41" s="185"/>
-      <c r="D41" s="186"/>
-      <c r="E41" s="186"/>
-      <c r="F41" s="186"/>
-      <c r="G41" s="196"/>
-      <c r="H41" s="186"/>
-      <c r="I41" s="220"/>
-      <c r="J41" s="220"/>
-      <c r="K41" s="204"/>
-      <c r="L41" s="190"/>
-      <c r="M41" s="220"/>
-      <c r="N41" s="211"/>
-      <c r="O41" s="211"/>
-      <c r="P41" s="211"/>
-      <c r="Q41" s="221"/>
+      <c r="A41" s="220"/>
+      <c r="B41" s="202"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="197"/>
+      <c r="H41" s="187"/>
+      <c r="I41" s="221"/>
+      <c r="J41" s="221"/>
+      <c r="K41" s="205"/>
+      <c r="L41" s="191"/>
+      <c r="M41" s="221"/>
+      <c r="N41" s="212"/>
+      <c r="O41" s="212"/>
+      <c r="P41" s="212"/>
+      <c r="Q41" s="222"/>
     </row>
     <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="219"/>
-      <c r="B42" s="184"/>
-      <c r="C42" s="225"/>
-      <c r="D42" s="226"/>
-      <c r="E42" s="186"/>
-      <c r="F42" s="186"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="186"/>
-      <c r="I42" s="186"/>
-      <c r="J42" s="186"/>
-      <c r="K42" s="204"/>
-      <c r="L42" s="190"/>
-      <c r="M42" s="211"/>
-      <c r="N42" s="211"/>
-      <c r="O42" s="211"/>
-      <c r="P42" s="211"/>
-      <c r="Q42" s="221"/>
+      <c r="A42" s="220"/>
+      <c r="B42" s="185"/>
+      <c r="C42" s="226"/>
+      <c r="D42" s="227"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="221"/>
+      <c r="H42" s="187"/>
+      <c r="I42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="205"/>
+      <c r="L42" s="191"/>
+      <c r="M42" s="212"/>
+      <c r="N42" s="212"/>
+      <c r="O42" s="212"/>
+      <c r="P42" s="212"/>
+      <c r="Q42" s="222"/>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="219"/>
-      <c r="B43" s="201"/>
-      <c r="C43" s="227"/>
-      <c r="D43" s="220"/>
-      <c r="E43" s="186"/>
-      <c r="F43" s="186"/>
-      <c r="G43" s="220"/>
-      <c r="H43" s="186"/>
-      <c r="I43" s="186"/>
-      <c r="J43" s="186"/>
-      <c r="K43" s="204"/>
-      <c r="L43" s="190"/>
-      <c r="M43" s="211"/>
-      <c r="N43" s="211"/>
-      <c r="O43" s="211"/>
-      <c r="P43" s="211"/>
-      <c r="Q43" s="221"/>
+      <c r="A43" s="220"/>
+      <c r="B43" s="202"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="221"/>
+      <c r="E43" s="187"/>
+      <c r="F43" s="187"/>
+      <c r="G43" s="221"/>
+      <c r="H43" s="187"/>
+      <c r="I43" s="187"/>
+      <c r="J43" s="187"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="212"/>
+      <c r="N43" s="212"/>
+      <c r="O43" s="212"/>
+      <c r="P43" s="212"/>
+      <c r="Q43" s="222"/>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="222"/>
-      <c r="B44" s="207"/>
-      <c r="C44" s="228"/>
-      <c r="D44" s="220"/>
-      <c r="E44" s="186"/>
-      <c r="F44" s="186"/>
-      <c r="G44" s="220"/>
-      <c r="H44" s="186"/>
-      <c r="I44" s="186"/>
-      <c r="J44" s="186"/>
-      <c r="K44" s="204"/>
-      <c r="L44" s="190"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="211"/>
-      <c r="Q44" s="221"/>
+      <c r="A44" s="223"/>
+      <c r="B44" s="208"/>
+      <c r="C44" s="229"/>
+      <c r="D44" s="221"/>
+      <c r="E44" s="187"/>
+      <c r="F44" s="187"/>
+      <c r="G44" s="221"/>
+      <c r="H44" s="187"/>
+      <c r="I44" s="187"/>
+      <c r="J44" s="187"/>
+      <c r="K44" s="205"/>
+      <c r="L44" s="191"/>
+      <c r="M44" s="212"/>
+      <c r="N44" s="212"/>
+      <c r="O44" s="212"/>
+      <c r="P44" s="212"/>
+      <c r="Q44" s="222"/>
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="229"/>
-      <c r="B45" s="207"/>
-      <c r="C45" s="228"/>
-      <c r="D45" s="220"/>
-      <c r="E45" s="186"/>
-      <c r="F45" s="186"/>
-      <c r="G45" s="220"/>
-      <c r="H45" s="186"/>
-      <c r="I45" s="186"/>
-      <c r="J45" s="186"/>
-      <c r="K45" s="204"/>
-      <c r="L45" s="190"/>
-      <c r="M45" s="211"/>
-      <c r="N45" s="211"/>
-      <c r="O45" s="211"/>
-      <c r="P45" s="211"/>
-      <c r="Q45" s="221"/>
+      <c r="A45" s="230"/>
+      <c r="B45" s="208"/>
+      <c r="C45" s="229"/>
+      <c r="D45" s="221"/>
+      <c r="E45" s="187"/>
+      <c r="F45" s="187"/>
+      <c r="G45" s="221"/>
+      <c r="H45" s="187"/>
+      <c r="I45" s="187"/>
+      <c r="J45" s="187"/>
+      <c r="K45" s="205"/>
+      <c r="L45" s="191"/>
+      <c r="M45" s="212"/>
+      <c r="N45" s="212"/>
+      <c r="O45" s="212"/>
+      <c r="P45" s="212"/>
+      <c r="Q45" s="222"/>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="211"/>
-      <c r="B46" s="230"/>
-      <c r="C46" s="225"/>
-      <c r="D46" s="220"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="186"/>
-      <c r="G46" s="220"/>
-      <c r="H46" s="186"/>
-      <c r="I46" s="186"/>
-      <c r="J46" s="186"/>
-      <c r="K46" s="204"/>
-      <c r="L46" s="190"/>
-      <c r="M46" s="211"/>
-      <c r="N46" s="211"/>
-      <c r="O46" s="211"/>
-      <c r="P46" s="211"/>
-      <c r="Q46" s="221"/>
+      <c r="A46" s="212"/>
+      <c r="B46" s="231"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="221"/>
+      <c r="E46" s="187"/>
+      <c r="F46" s="187"/>
+      <c r="G46" s="221"/>
+      <c r="H46" s="187"/>
+      <c r="I46" s="187"/>
+      <c r="J46" s="187"/>
+      <c r="K46" s="205"/>
+      <c r="L46" s="191"/>
+      <c r="M46" s="212"/>
+      <c r="N46" s="212"/>
+      <c r="O46" s="212"/>
+      <c r="P46" s="212"/>
+      <c r="Q46" s="222"/>
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="222"/>
-      <c r="B47" s="201"/>
-      <c r="C47" s="227"/>
-      <c r="D47" s="220"/>
-      <c r="E47" s="186"/>
-      <c r="F47" s="186"/>
-      <c r="G47" s="220"/>
-      <c r="H47" s="186"/>
-      <c r="I47" s="186"/>
-      <c r="J47" s="186"/>
-      <c r="K47" s="204"/>
-      <c r="L47" s="190"/>
-      <c r="M47" s="211"/>
-      <c r="N47" s="211"/>
-      <c r="O47" s="211"/>
-      <c r="P47" s="211"/>
-      <c r="Q47" s="221"/>
+      <c r="A47" s="223"/>
+      <c r="B47" s="202"/>
+      <c r="C47" s="228"/>
+      <c r="D47" s="221"/>
+      <c r="E47" s="187"/>
+      <c r="F47" s="187"/>
+      <c r="G47" s="221"/>
+      <c r="H47" s="187"/>
+      <c r="I47" s="187"/>
+      <c r="J47" s="187"/>
+      <c r="K47" s="205"/>
+      <c r="L47" s="191"/>
+      <c r="M47" s="212"/>
+      <c r="N47" s="212"/>
+      <c r="O47" s="212"/>
+      <c r="P47" s="212"/>
+      <c r="Q47" s="222"/>
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="211"/>
-      <c r="B48" s="230"/>
-      <c r="C48" s="228"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="186"/>
-      <c r="I48" s="186"/>
-      <c r="J48" s="186"/>
-      <c r="K48" s="204"/>
-      <c r="L48" s="190"/>
-      <c r="M48" s="211"/>
-      <c r="N48" s="211"/>
-      <c r="O48" s="211"/>
-      <c r="P48" s="211"/>
-      <c r="Q48" s="221"/>
+      <c r="A48" s="212"/>
+      <c r="B48" s="231"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="221"/>
+      <c r="E48" s="187"/>
+      <c r="F48" s="187"/>
+      <c r="G48" s="221"/>
+      <c r="H48" s="187"/>
+      <c r="I48" s="187"/>
+      <c r="J48" s="187"/>
+      <c r="K48" s="205"/>
+      <c r="L48" s="191"/>
+      <c r="M48" s="212"/>
+      <c r="N48" s="212"/>
+      <c r="O48" s="212"/>
+      <c r="P48" s="212"/>
+      <c r="Q48" s="222"/>
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="222"/>
-      <c r="B49" s="201"/>
-      <c r="C49" s="223"/>
-      <c r="D49" s="220"/>
-      <c r="E49" s="186"/>
-      <c r="F49" s="186"/>
-      <c r="G49" s="220"/>
-      <c r="H49" s="186"/>
-      <c r="I49" s="186"/>
-      <c r="J49" s="186"/>
-      <c r="K49" s="204"/>
-      <c r="L49" s="190"/>
-      <c r="M49" s="211"/>
-      <c r="N49" s="211"/>
-      <c r="O49" s="211"/>
-      <c r="P49" s="211"/>
-      <c r="Q49" s="221"/>
+      <c r="A49" s="223"/>
+      <c r="B49" s="202"/>
+      <c r="C49" s="224"/>
+      <c r="D49" s="221"/>
+      <c r="E49" s="187"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="221"/>
+      <c r="H49" s="187"/>
+      <c r="I49" s="187"/>
+      <c r="J49" s="187"/>
+      <c r="K49" s="205"/>
+      <c r="L49" s="191"/>
+      <c r="M49" s="212"/>
+      <c r="N49" s="212"/>
+      <c r="O49" s="212"/>
+      <c r="P49" s="212"/>
+      <c r="Q49" s="222"/>
     </row>
     <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="231"/>
-      <c r="B50" s="232"/>
-      <c r="C50" s="222"/>
-      <c r="D50" s="220"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="220"/>
-      <c r="H50" s="186"/>
-      <c r="I50" s="186"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="204"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="211"/>
-      <c r="N50" s="211"/>
-      <c r="O50" s="211"/>
-      <c r="P50" s="211"/>
-      <c r="Q50" s="221"/>
+      <c r="A50" s="232"/>
+      <c r="B50" s="233"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="221"/>
+      <c r="E50" s="187"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="221"/>
+      <c r="H50" s="187"/>
+      <c r="I50" s="187"/>
+      <c r="J50" s="187"/>
+      <c r="K50" s="205"/>
+      <c r="L50" s="191"/>
+      <c r="M50" s="212"/>
+      <c r="N50" s="212"/>
+      <c r="O50" s="212"/>
+      <c r="P50" s="212"/>
+      <c r="Q50" s="222"/>
     </row>
     <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="211"/>
-      <c r="B51" s="230"/>
-      <c r="C51" s="223"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="186"/>
-      <c r="F51" s="186"/>
-      <c r="G51" s="220"/>
-      <c r="H51" s="186"/>
-      <c r="I51" s="186"/>
-      <c r="J51" s="186"/>
-      <c r="K51" s="204"/>
-      <c r="L51" s="190"/>
-      <c r="M51" s="211"/>
-      <c r="N51" s="211"/>
-      <c r="O51" s="211"/>
-      <c r="P51" s="211"/>
-      <c r="Q51" s="221"/>
+      <c r="A51" s="212"/>
+      <c r="B51" s="231"/>
+      <c r="C51" s="224"/>
+      <c r="D51" s="221"/>
+      <c r="E51" s="187"/>
+      <c r="F51" s="187"/>
+      <c r="G51" s="221"/>
+      <c r="H51" s="187"/>
+      <c r="I51" s="187"/>
+      <c r="J51" s="187"/>
+      <c r="K51" s="205"/>
+      <c r="L51" s="191"/>
+      <c r="M51" s="212"/>
+      <c r="N51" s="212"/>
+      <c r="O51" s="212"/>
+      <c r="P51" s="212"/>
+      <c r="Q51" s="222"/>
     </row>
     <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="222"/>
-      <c r="B52" s="194"/>
-      <c r="C52" s="222"/>
-      <c r="D52" s="220"/>
-      <c r="E52" s="186"/>
-      <c r="F52" s="186"/>
-      <c r="G52" s="220"/>
-      <c r="H52" s="186"/>
-      <c r="I52" s="186"/>
-      <c r="J52" s="186"/>
-      <c r="K52" s="204"/>
-      <c r="L52" s="190"/>
-      <c r="M52" s="211"/>
-      <c r="N52" s="211"/>
-      <c r="O52" s="211"/>
-      <c r="P52" s="211"/>
-      <c r="Q52" s="221"/>
+      <c r="A52" s="223"/>
+      <c r="B52" s="195"/>
+      <c r="C52" s="223"/>
+      <c r="D52" s="221"/>
+      <c r="E52" s="187"/>
+      <c r="F52" s="187"/>
+      <c r="G52" s="221"/>
+      <c r="H52" s="187"/>
+      <c r="I52" s="187"/>
+      <c r="J52" s="187"/>
+      <c r="K52" s="205"/>
+      <c r="L52" s="191"/>
+      <c r="M52" s="212"/>
+      <c r="N52" s="212"/>
+      <c r="O52" s="212"/>
+      <c r="P52" s="212"/>
+      <c r="Q52" s="222"/>
     </row>
     <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="229"/>
-      <c r="B53" s="201"/>
-      <c r="C53" s="229"/>
-      <c r="D53" s="220"/>
-      <c r="E53" s="186"/>
-      <c r="F53" s="186"/>
-      <c r="G53" s="220"/>
-      <c r="H53" s="186"/>
-      <c r="I53" s="186"/>
-      <c r="J53" s="186"/>
-      <c r="K53" s="204"/>
-      <c r="L53" s="190"/>
-      <c r="M53" s="211"/>
-      <c r="N53" s="211"/>
-      <c r="O53" s="211"/>
-      <c r="P53" s="211"/>
-      <c r="Q53" s="221"/>
+      <c r="A53" s="230"/>
+      <c r="B53" s="202"/>
+      <c r="C53" s="230"/>
+      <c r="D53" s="221"/>
+      <c r="E53" s="187"/>
+      <c r="F53" s="187"/>
+      <c r="G53" s="221"/>
+      <c r="H53" s="187"/>
+      <c r="I53" s="187"/>
+      <c r="J53" s="187"/>
+      <c r="K53" s="205"/>
+      <c r="L53" s="191"/>
+      <c r="M53" s="212"/>
+      <c r="N53" s="212"/>
+      <c r="O53" s="212"/>
+      <c r="P53" s="212"/>
+      <c r="Q53" s="222"/>
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="229"/>
-      <c r="B54" s="207"/>
-      <c r="C54" s="223"/>
-      <c r="D54" s="220"/>
-      <c r="E54" s="186"/>
-      <c r="F54" s="186"/>
-      <c r="G54" s="220"/>
-      <c r="H54" s="186"/>
-      <c r="I54" s="186"/>
-      <c r="J54" s="186"/>
-      <c r="K54" s="204"/>
-      <c r="L54" s="190"/>
-      <c r="M54" s="211"/>
-      <c r="N54" s="211"/>
-      <c r="O54" s="211"/>
-      <c r="P54" s="211"/>
-      <c r="Q54" s="221"/>
+      <c r="A54" s="230"/>
+      <c r="B54" s="208"/>
+      <c r="C54" s="224"/>
+      <c r="D54" s="221"/>
+      <c r="E54" s="187"/>
+      <c r="F54" s="187"/>
+      <c r="G54" s="221"/>
+      <c r="H54" s="187"/>
+      <c r="I54" s="187"/>
+      <c r="J54" s="187"/>
+      <c r="K54" s="205"/>
+      <c r="L54" s="191"/>
+      <c r="M54" s="212"/>
+      <c r="N54" s="212"/>
+      <c r="O54" s="212"/>
+      <c r="P54" s="212"/>
+      <c r="Q54" s="222"/>
     </row>
     <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="229"/>
-      <c r="B55" s="207"/>
-      <c r="C55" s="222"/>
-      <c r="D55" s="220"/>
-      <c r="E55" s="186"/>
-      <c r="F55" s="186"/>
-      <c r="G55" s="220"/>
-      <c r="H55" s="186"/>
-      <c r="I55" s="186"/>
-      <c r="J55" s="186"/>
-      <c r="K55" s="204"/>
-      <c r="L55" s="190"/>
-      <c r="M55" s="211"/>
-      <c r="N55" s="211"/>
-      <c r="O55" s="211"/>
-      <c r="P55" s="211"/>
-      <c r="Q55" s="221"/>
+      <c r="A55" s="230"/>
+      <c r="B55" s="208"/>
+      <c r="C55" s="223"/>
+      <c r="D55" s="221"/>
+      <c r="E55" s="187"/>
+      <c r="F55" s="187"/>
+      <c r="G55" s="221"/>
+      <c r="H55" s="187"/>
+      <c r="I55" s="187"/>
+      <c r="J55" s="187"/>
+      <c r="K55" s="205"/>
+      <c r="L55" s="191"/>
+      <c r="M55" s="212"/>
+      <c r="N55" s="212"/>
+      <c r="O55" s="212"/>
+      <c r="P55" s="212"/>
+      <c r="Q55" s="222"/>
     </row>
     <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="231"/>
-      <c r="B56" s="230"/>
-      <c r="C56" s="229"/>
-      <c r="D56" s="220"/>
-      <c r="E56" s="186"/>
-      <c r="F56" s="186"/>
-      <c r="G56" s="220"/>
-      <c r="H56" s="186"/>
-      <c r="I56" s="186"/>
-      <c r="J56" s="186"/>
-      <c r="K56" s="204"/>
-      <c r="L56" s="190"/>
-      <c r="M56" s="211"/>
-      <c r="N56" s="211"/>
-      <c r="O56" s="211"/>
-      <c r="P56" s="211"/>
-      <c r="Q56" s="221"/>
+      <c r="A56" s="232"/>
+      <c r="B56" s="231"/>
+      <c r="C56" s="230"/>
+      <c r="D56" s="221"/>
+      <c r="E56" s="187"/>
+      <c r="F56" s="187"/>
+      <c r="G56" s="221"/>
+      <c r="H56" s="187"/>
+      <c r="I56" s="187"/>
+      <c r="J56" s="187"/>
+      <c r="K56" s="205"/>
+      <c r="L56" s="191"/>
+      <c r="M56" s="212"/>
+      <c r="N56" s="212"/>
+      <c r="O56" s="212"/>
+      <c r="P56" s="212"/>
+      <c r="Q56" s="222"/>
     </row>
     <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="229"/>
-      <c r="B57" s="201"/>
-      <c r="C57" s="229"/>
-      <c r="D57" s="220"/>
-      <c r="E57" s="186"/>
-      <c r="F57" s="186"/>
-      <c r="G57" s="186"/>
-      <c r="H57" s="186"/>
-      <c r="I57" s="186"/>
-      <c r="J57" s="186"/>
-      <c r="K57" s="220"/>
-      <c r="L57" s="190"/>
-      <c r="M57" s="211"/>
-      <c r="N57" s="211"/>
-      <c r="O57" s="211"/>
-      <c r="P57" s="211"/>
-      <c r="Q57" s="221"/>
+      <c r="A57" s="230"/>
+      <c r="B57" s="202"/>
+      <c r="C57" s="230"/>
+      <c r="D57" s="221"/>
+      <c r="E57" s="187"/>
+      <c r="F57" s="187"/>
+      <c r="G57" s="187"/>
+      <c r="H57" s="187"/>
+      <c r="I57" s="187"/>
+      <c r="J57" s="187"/>
+      <c r="K57" s="221"/>
+      <c r="L57" s="191"/>
+      <c r="M57" s="212"/>
+      <c r="N57" s="212"/>
+      <c r="O57" s="212"/>
+      <c r="P57" s="212"/>
+      <c r="Q57" s="222"/>
     </row>
     <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="223"/>
-      <c r="B58" s="207"/>
-      <c r="C58" s="225"/>
-      <c r="D58" s="220"/>
-      <c r="E58" s="186"/>
-      <c r="F58" s="186"/>
-      <c r="G58" s="186"/>
-      <c r="H58" s="186"/>
-      <c r="I58" s="186"/>
-      <c r="J58" s="186"/>
-      <c r="K58" s="220"/>
-      <c r="L58" s="190"/>
-      <c r="M58" s="211"/>
-      <c r="N58" s="211"/>
-      <c r="O58" s="211"/>
-      <c r="P58" s="211"/>
-      <c r="Q58" s="221"/>
+      <c r="A58" s="224"/>
+      <c r="B58" s="208"/>
+      <c r="C58" s="226"/>
+      <c r="D58" s="221"/>
+      <c r="E58" s="187"/>
+      <c r="F58" s="187"/>
+      <c r="G58" s="187"/>
+      <c r="H58" s="187"/>
+      <c r="I58" s="187"/>
+      <c r="J58" s="187"/>
+      <c r="K58" s="221"/>
+      <c r="L58" s="191"/>
+      <c r="M58" s="212"/>
+      <c r="N58" s="212"/>
+      <c r="O58" s="212"/>
+      <c r="P58" s="212"/>
+      <c r="Q58" s="222"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="233"/>
-      <c r="B59" s="233"/>
-      <c r="C59" s="233"/>
-      <c r="D59" s="234"/>
-      <c r="E59" s="234"/>
-      <c r="F59" s="234"/>
-      <c r="G59" s="234"/>
-      <c r="H59" s="234"/>
-      <c r="I59" s="234"/>
-      <c r="J59" s="234"/>
-      <c r="K59" s="234"/>
-      <c r="L59" s="234"/>
-      <c r="M59" s="234"/>
-      <c r="N59" s="234"/>
-      <c r="O59" s="234"/>
-      <c r="P59" s="234"/>
+      <c r="A59" s="234"/>
+      <c r="B59" s="234"/>
+      <c r="C59" s="234"/>
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+      <c r="H59" s="235"/>
+      <c r="I59" s="235"/>
+      <c r="J59" s="235"/>
+      <c r="K59" s="235"/>
+      <c r="L59" s="235"/>
+      <c r="M59" s="235"/>
+      <c r="N59" s="235"/>
+      <c r="O59" s="235"/>
+      <c r="P59" s="235"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="233"/>
-      <c r="B60" s="233"/>
-      <c r="C60" s="233"/>
-      <c r="D60" s="234"/>
-      <c r="E60" s="234"/>
-      <c r="F60" s="234"/>
-      <c r="G60" s="234"/>
-      <c r="H60" s="234"/>
-      <c r="I60" s="234"/>
-      <c r="J60" s="234"/>
-      <c r="K60" s="234"/>
-      <c r="L60" s="234"/>
-      <c r="M60" s="234"/>
-      <c r="N60" s="234"/>
-      <c r="O60" s="234"/>
-      <c r="P60" s="234"/>
+      <c r="A60" s="234"/>
+      <c r="B60" s="234"/>
+      <c r="C60" s="234"/>
+      <c r="D60" s="235"/>
+      <c r="E60" s="235"/>
+      <c r="F60" s="235"/>
+      <c r="G60" s="235"/>
+      <c r="H60" s="235"/>
+      <c r="I60" s="235"/>
+      <c r="J60" s="235"/>
+      <c r="K60" s="235"/>
+      <c r="L60" s="235"/>
+      <c r="M60" s="235"/>
+      <c r="N60" s="235"/>
+      <c r="O60" s="235"/>
+      <c r="P60" s="235"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="233"/>
-      <c r="B61" s="233"/>
-      <c r="C61" s="233"/>
-      <c r="D61" s="234"/>
-      <c r="E61" s="234"/>
-      <c r="F61" s="234"/>
-      <c r="G61" s="234"/>
-      <c r="H61" s="234"/>
-      <c r="I61" s="234"/>
-      <c r="J61" s="234"/>
-      <c r="K61" s="234"/>
-      <c r="L61" s="234"/>
-      <c r="M61" s="234"/>
-      <c r="N61" s="234"/>
-      <c r="O61" s="234"/>
-      <c r="P61" s="234"/>
+      <c r="A61" s="234"/>
+      <c r="B61" s="234"/>
+      <c r="C61" s="234"/>
+      <c r="D61" s="235"/>
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="235"/>
+      <c r="H61" s="235"/>
+      <c r="I61" s="235"/>
+      <c r="J61" s="235"/>
+      <c r="K61" s="235"/>
+      <c r="L61" s="235"/>
+      <c r="M61" s="235"/>
+      <c r="N61" s="235"/>
+      <c r="O61" s="235"/>
+      <c r="P61" s="235"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5104,107 +5128,111 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="102" width="27.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="102" width="31.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="102" width="31.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="102" width="24.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="102" width="30.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="102" width="52.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="236" width="52.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="102" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="111" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="235" t="s">
+    <row r="1" s="111" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="237" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="235" t="s">
+      <c r="B1" s="237" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="235" t="s">
-        <v>206</v>
-      </c>
-      <c r="D1" s="235" t="s">
-        <v>207</v>
-      </c>
-      <c r="E1" s="235" t="s">
+      <c r="C1" s="237" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="237" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="238" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="236" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="236" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="237" t="s">
+      <c r="A2" s="239" t="s">
         <v>210</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="238" t="s">
+      <c r="B2" s="239" t="s">
         <v>211</v>
       </c>
+      <c r="C2" s="240" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="240"/>
+      <c r="E2" s="241" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="236" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" s="236" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="238" t="s">
+      <c r="A3" s="239" t="s">
         <v>214</v>
       </c>
+      <c r="B3" s="239" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="241" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="236" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="236" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="237" t="s">
+      <c r="A4" s="239" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="237" t="s">
+      <c r="B4" s="239" t="s">
         <v>218</v>
       </c>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="240" t="s">
         <v>219</v>
       </c>
+      <c r="D4" s="240" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="241" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="239" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" s="239" t="s">
-        <v>221</v>
-      </c>
-      <c r="C5" s="240" t="s">
+      <c r="A5" s="242" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="239"/>
-      <c r="E5" s="238" t="s">
+      <c r="B5" s="242" t="s">
         <v>223</v>
       </c>
+      <c r="C5" s="243" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="242"/>
+      <c r="E5" s="241" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="239" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="239"/>
-      <c r="C6" s="239"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="238" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="239"/>
-      <c r="B7" s="239"/>
-      <c r="C7" s="239"/>
-      <c r="D7" s="239"/>
-      <c r="E7" s="239"/>
+      <c r="A6" s="242" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="242"/>
+      <c r="C6" s="242"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="241" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="242" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="242"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="241" t="s">
+        <v>229</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5241,15 +5269,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="26.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="17" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="18" width="32.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="18" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="18" width="5.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="18" width="18.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="18" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="18" width="5.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="18" width="22.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="18" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="18" width="5.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="18" width="25.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="18" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="18" width="5.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="18" width="41.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="18" width="5.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="18" width="5.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="18" width="43.63"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="29" min="26" style="18" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="30" style="19" width="11"/>
@@ -6196,7 +6224,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="39" width="26.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="39" width="147.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="39" width="42.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="39" width="43.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="39" width="43.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="53.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="17.37"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="20" width="9.37"/>
@@ -6320,7 +6348,7 @@
       <c r="E8" s="43"/>
       <c r="F8" s="44"/>
     </row>
-    <row r="9" customFormat="false" ht="17.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
         <v>62</v>
       </c>
@@ -6817,8 +6845,12 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>129</v>
+      </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -6896,13 +6928,13 @@
         <v>27</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C1" s="54" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E1" s="52" t="s">
         <v>28</v>
@@ -6917,157 +6949,157 @@
         <v>31</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="58"/>
       <c r="D2" s="56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H2" s="56"/>
       <c r="I2" s="60" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="57"/>
       <c r="D3" s="61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E3" s="56" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F3" s="56"/>
       <c r="G3" s="62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H3" s="56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I3" s="60" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" s="56"/>
       <c r="D4" s="61" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F4" s="56"/>
       <c r="G4" s="56" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H4" s="56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I4" s="60" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="56" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" s="61" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" s="56" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F5" s="56"/>
       <c r="G5" s="56" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H5" s="56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I5" s="60" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F6" s="56"/>
       <c r="G6" s="56" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H6" s="56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I6" s="60" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D7" s="61" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F7" s="56"/>
       <c r="G7" s="56" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H7" s="56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7208,10 +7240,10 @@
         <v>27</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,16 +7287,16 @@
         <v>28</v>
       </c>
       <c r="C1" s="70" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D1" s="71" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E1" s="70" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
@@ -7340,35 +7372,35 @@
         <v>28</v>
       </c>
       <c r="D1" s="92" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" s="97" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="94" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B2" s="94" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C2" s="95" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D2" s="96" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" s="97" customFormat="true" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="98" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B3" s="98" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C3" s="99" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7562,19 +7594,19 @@
         <v>28</v>
       </c>
       <c r="C1" s="105" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D1" s="106" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E1" s="107" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F1" s="108" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" s="104" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" s="109"/>
       <c r="I1" s="110"/>
@@ -7582,7 +7614,7 @@
       <c r="K1" s="110"/>
       <c r="L1" s="110"/>
     </row>
-    <row r="2" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="112"/>
       <c r="B2" s="113"/>
       <c r="C2" s="114"/>
@@ -7596,7 +7628,7 @@
       <c r="K2" s="118"/>
       <c r="L2" s="118"/>
     </row>
-    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="119"/>
       <c r="B3" s="120"/>
       <c r="C3" s="121"/>
